--- a/Measurements/17058PP Blade Bolt/17058PP.xlsx
+++ b/Measurements/17058PP Blade Bolt/17058PP.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoe\Meng\solidworks\Measurements\17058PP Blade Bolt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFDD34A7-C223-4411-A334-CC01C45AED1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01341725-C8FE-4BB3-8864-08385752B211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="records" sheetId="18" r:id="rId1"/>
+    <sheet name="records (2)" sheetId="21" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">records!$B$1:$P$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'records (2)'!$B$1:$P$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="30">
   <si>
     <t>Sample Measurement Record</t>
   </si>
@@ -120,6 +122,12 @@
   </si>
   <si>
     <t>0.682</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
 </sst>
 </file>
@@ -633,7 +641,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -793,10 +801,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2348,6 +2374,1683 @@
             </a:rPr>
             <a:t>L</a:t>
           </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>28574</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>272845</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AC5568E-FAF8-4B27-8E2C-B4573BAAC786}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="628649" y="2381250"/>
+          <a:ext cx="5216321" cy="3838575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>22877</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>209551</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B8F0B81-1A25-4828-BBE1-861659FEE751}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5629275" y="2428876"/>
+          <a:ext cx="2870852" cy="1866900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>10219</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAC2E040-1D1A-48C8-8707-C9E298215275}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9677400" y="7973119"/>
+          <a:ext cx="184731" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:srgbClr val="00B050"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>47649</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="342786"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="TextBox 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C5419CC-2A7C-47BE-9039-80D9ADE58759}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9677400" y="7010424"/>
+          <a:ext cx="184731" cy="342786"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1600" b="1">
+            <a:solidFill>
+              <a:srgbClr val="00B050"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>68706</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="342786"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E8754B0-8490-4C56-B290-CD2F7EB3C9BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9677400" y="9460356"/>
+          <a:ext cx="184731" cy="342786"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1600" b="1">
+            <a:solidFill>
+              <a:srgbClr val="00B050"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>37290</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="342786"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="TextBox 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93DB88E8-B3E3-41B2-9428-B59093E1C022}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9677400" y="7000065"/>
+          <a:ext cx="184731" cy="342786"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1600" b="1">
+            <a:solidFill>
+              <a:srgbClr val="00B050"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>30940</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="342786"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="TextBox 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D040BD8-96F3-458C-814C-E7FA76FA7937}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9677400" y="6707965"/>
+          <a:ext cx="184731" cy="342786"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1600" b="1">
+            <a:solidFill>
+              <a:srgbClr val="00B050"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>49631</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>91741</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="342786"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="TextBox 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{303FE939-9E63-414C-B1B5-883FA8C83FCD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2135606" y="2444416"/>
+          <a:ext cx="184731" cy="342786"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1600" b="1">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>275056</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>2172</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="342786"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="TextBox 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E79E3A17-6A33-4285-94FF-0B7A02274884}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="875131" y="4336047"/>
+          <a:ext cx="184731" cy="342786"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1600" b="1">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>234449</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>219577</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="342786"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="TextBox 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CDC693D-30B4-405F-A6C8-373FBD9CB0D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8711699" y="4305802"/>
+          <a:ext cx="184731" cy="342786"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1600" b="1">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>94582</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>247649</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="342786"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="TextBox 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FE6FA5C-6249-4A93-8F58-B8B1EAFD2FC6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3923632" y="4829174"/>
+          <a:ext cx="184731" cy="342786"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1600" b="1">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>56482</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>19049</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="342786"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="TextBox 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2EC952E-D651-471B-AEF5-7FEAB4C8A0E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4466557" y="4352924"/>
+          <a:ext cx="184731" cy="342786"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1600" b="1">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="374141"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="TextBox 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C396514D-6837-41BB-A55E-F5084DCEFB7C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4267200" y="5248275"/>
+          <a:ext cx="184731" cy="374141"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1800" b="1">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="293478" cy="311496"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="TextBox 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B29D1556-044F-4207-966E-3A72DEF8332E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="762000" y="5715000"/>
+          <a:ext cx="293478" cy="311496"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>A</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="285335" cy="311496"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="TextBox 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50F5D7FE-2BAC-46BF-8C0A-ACE45AE26C71}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="895350" y="3248025"/>
+          <a:ext cx="285335" cy="311496"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>B</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="279692" cy="311496"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="TextBox 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7ED7850-9EA6-430D-8D67-3582306263FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1152525" y="2686050"/>
+          <a:ext cx="279692" cy="311496"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>C</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="297838" cy="311496"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="TextBox 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A82C0901-9F91-4EC6-8A04-382A0ABC8DA9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2876550" y="2781300"/>
+          <a:ext cx="297838" cy="311496"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>D</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="272254" cy="311496"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="TextBox 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BB400F9-2B29-4AF5-BC9C-5E2EBB58635F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2381250" y="2276475"/>
+          <a:ext cx="272254" cy="311496"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>E</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="267061" cy="311496"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="TextBox 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34DED0A6-D870-4712-9153-24A9994E20A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4267200" y="4667250"/>
+          <a:ext cx="267061" cy="311496"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>F</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="299056" cy="311496"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="TextBox 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75A0937B-14C1-4472-B1EF-7B4FA3B884D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5743575" y="2524125"/>
+          <a:ext cx="299056" cy="311496"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>G</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="297902" cy="311496"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="TextBox 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEC72395-CD37-4E79-94AF-14B4B9C0E886}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7915275" y="2752725"/>
+          <a:ext cx="297902" cy="311496"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>H</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>238125</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="232500" cy="311496"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="TextBox 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CBE01D5-E584-4772-ACE8-2776586DF19B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4743450" y="5067300"/>
+          <a:ext cx="232500" cy="311496"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>I</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="244106" cy="311496"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="TextBox 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEE0812B-B127-4080-ABB2-46395CDBC95E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2409825" y="5991225"/>
+          <a:ext cx="244106" cy="311496"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>J</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>238125</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="282834" cy="311496"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="TextBox 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A602E9A-D321-4EC9-8E11-9A55D49616CC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3648075" y="5562600"/>
+          <a:ext cx="282834" cy="311496"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>K</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>238125</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>524073</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>104865</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="Picture 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E972562F-E36A-44C0-94F0-95F1ACB6CB2B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7581900" y="5562600"/>
+          <a:ext cx="1419423" cy="647790"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="260584" cy="311496"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="TextBox 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCB81098-140C-4327-8F6E-DFAD5BCFD422}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3162300" y="5124450"/>
+          <a:ext cx="260584" cy="311496"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>L</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="341568" cy="311496"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="TextBox 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47EB241B-9322-46D5-B1D8-84031B4CE27E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5705475" y="3962400"/>
+          <a:ext cx="341568" cy="311496"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>M</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2317814" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="TextBox 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6C300C5-68CC-20A4-C6A7-F344D3779EC8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5991225" y="4362450"/>
+          <a:ext cx="2317814" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Note:</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> "M" can't be measured reliably</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2626,23 +4329,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:20" ht="30" customHeight="1">
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
       <c r="Q1" s="17"/>
     </row>
     <row r="2" spans="2:20" ht="26.45" customHeight="1" thickBot="1">
@@ -2792,7 +4495,7 @@
       <c r="L5" s="44">
         <v>5.45E-2</v>
       </c>
-      <c r="M5" s="54">
+      <c r="M5" s="53">
         <v>4.4499999999999998E-2</v>
       </c>
       <c r="N5" s="52">
@@ -2882,7 +4585,7 @@
       <c r="L7" s="44">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="M7" s="54">
+      <c r="M7" s="53">
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="N7" s="52">
@@ -3440,4 +5143,839 @@
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4E4926-E574-4AC4-82E7-930D5108290A}">
+  <dimension ref="B1:AA36"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="4.85546875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="8.7109375" style="12" customWidth="1"/>
+    <col min="5" max="16" width="8.7109375" style="1" customWidth="1"/>
+    <col min="17" max="18" width="9.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:27" ht="30" customHeight="1">
+      <c r="B1" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="17"/>
+    </row>
+    <row r="2" spans="2:27" ht="26.45" customHeight="1" thickBot="1">
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q2" s="18"/>
+    </row>
+    <row r="3" spans="2:27" ht="24.95" customHeight="1" thickTop="1">
+      <c r="B3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="19"/>
+      <c r="T3" s="16"/>
+    </row>
+    <row r="4" spans="2:27" ht="20.100000000000001" customHeight="1">
+      <c r="B4" s="7">
+        <v>1</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="44">
+        <v>1.032</v>
+      </c>
+      <c r="F4" s="49">
+        <v>2.375</v>
+      </c>
+      <c r="G4" s="49">
+        <v>2.62</v>
+      </c>
+      <c r="H4" s="49">
+        <v>1.375</v>
+      </c>
+      <c r="I4" s="49">
+        <v>2.9940000000000002</v>
+      </c>
+      <c r="J4" s="49">
+        <v>2.0045000000000002</v>
+      </c>
+      <c r="K4" s="49">
+        <v>0.246</v>
+      </c>
+      <c r="L4" s="55">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="M4" s="55">
+        <v>0.05</v>
+      </c>
+      <c r="N4" s="58">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="O4" s="26"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="21"/>
+    </row>
+    <row r="5" spans="2:27" ht="20.100000000000001" customHeight="1">
+      <c r="B5" s="7">
+        <v>2</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="44">
+        <v>1.0295000000000001</v>
+      </c>
+      <c r="F5" s="44">
+        <v>2.3719999999999999</v>
+      </c>
+      <c r="G5" s="44">
+        <v>2.637</v>
+      </c>
+      <c r="H5" s="49">
+        <v>1.3779999999999999</v>
+      </c>
+      <c r="I5" s="44">
+        <v>3.0049999999999999</v>
+      </c>
+      <c r="J5" s="44">
+        <v>2.0049999999999999</v>
+      </c>
+      <c r="K5" s="44">
+        <v>0.246</v>
+      </c>
+      <c r="L5" s="56">
+        <v>5.45E-2</v>
+      </c>
+      <c r="M5" s="53">
+        <v>4.4499999999999998E-2</v>
+      </c>
+      <c r="N5" s="59">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="O5" s="25"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="23"/>
+    </row>
+    <row r="6" spans="2:27" ht="20.100000000000001" customHeight="1">
+      <c r="B6" s="7">
+        <v>3</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="44">
+        <v>1.026</v>
+      </c>
+      <c r="F6" s="44">
+        <v>2.383</v>
+      </c>
+      <c r="G6" s="44">
+        <v>2.6259999999999999</v>
+      </c>
+      <c r="H6" s="49">
+        <v>1.377</v>
+      </c>
+      <c r="I6" s="44">
+        <v>2.9984999999999999</v>
+      </c>
+      <c r="J6" s="44">
+        <v>2.0049999999999999</v>
+      </c>
+      <c r="K6" s="44">
+        <v>0.247</v>
+      </c>
+      <c r="L6" s="56">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="M6" s="55">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="N6" s="59">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="O6" s="25"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="23"/>
+    </row>
+    <row r="7" spans="2:27" ht="20.100000000000001" customHeight="1">
+      <c r="B7" s="7">
+        <v>4</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="44">
+        <v>1.028</v>
+      </c>
+      <c r="F7" s="44">
+        <v>2.3849999999999998</v>
+      </c>
+      <c r="G7" s="44">
+        <v>2.63</v>
+      </c>
+      <c r="H7" s="49">
+        <v>1.3779999999999999</v>
+      </c>
+      <c r="I7" s="44">
+        <v>2.9990000000000001</v>
+      </c>
+      <c r="J7" s="44">
+        <v>2.0034999999999998</v>
+      </c>
+      <c r="K7" s="44">
+        <v>0.248</v>
+      </c>
+      <c r="L7" s="56">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="M7" s="53">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="N7" s="59">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="O7" s="25"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="23"/>
+    </row>
+    <row r="8" spans="2:27" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="B8" s="15">
+        <v>5</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="48">
+        <v>1.0255000000000001</v>
+      </c>
+      <c r="F8" s="48">
+        <v>2.3889999999999998</v>
+      </c>
+      <c r="G8" s="50">
+        <v>2.6429999999999998</v>
+      </c>
+      <c r="H8" s="50">
+        <v>1.3714999999999999</v>
+      </c>
+      <c r="I8" s="50">
+        <v>2.9990000000000001</v>
+      </c>
+      <c r="J8" s="50">
+        <v>2.004</v>
+      </c>
+      <c r="K8" s="50">
+        <v>0.247</v>
+      </c>
+      <c r="L8" s="57">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="M8" s="57">
+        <v>5.5E-2</v>
+      </c>
+      <c r="N8" s="60">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="O8" s="29"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="15"/>
+      <c r="R8" s="24"/>
+    </row>
+    <row r="9" spans="2:27" ht="6.75" customHeight="1" thickTop="1"/>
+    <row r="10" spans="2:27" ht="20.100000000000001" customHeight="1">
+      <c r="B10" s="31"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="34"/>
+      <c r="Q10" s="8"/>
+    </row>
+    <row r="11" spans="2:27" ht="20.100000000000001" customHeight="1">
+      <c r="B11" s="35"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="8"/>
+      <c r="T11" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:27" ht="20.100000000000001" customHeight="1">
+      <c r="B12" s="35"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="8"/>
+    </row>
+    <row r="13" spans="2:27" ht="20.100000000000001" customHeight="1">
+      <c r="B13" s="35"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="8"/>
+    </row>
+    <row r="14" spans="2:27" ht="20.100000000000001" customHeight="1">
+      <c r="B14" s="35"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="8"/>
+    </row>
+    <row r="15" spans="2:27" ht="20.100000000000001" customHeight="1">
+      <c r="B15" s="35"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="8"/>
+    </row>
+    <row r="16" spans="2:27" ht="20.100000000000001" customHeight="1">
+      <c r="B16" s="35"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="8"/>
+      <c r="AA16" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="2:23" ht="20.100000000000001" customHeight="1">
+      <c r="B17" s="35"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="8"/>
+    </row>
+    <row r="18" spans="2:23" ht="20.100000000000001" customHeight="1">
+      <c r="B18" s="35"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="8"/>
+      <c r="W18" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:23" ht="20.100000000000001" customHeight="1">
+      <c r="B19" s="35"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="8"/>
+    </row>
+    <row r="20" spans="2:23" ht="20.100000000000001" customHeight="1">
+      <c r="B20" s="35"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="8"/>
+    </row>
+    <row r="21" spans="2:23" ht="20.100000000000001" customHeight="1">
+      <c r="B21" s="35"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="8"/>
+    </row>
+    <row r="22" spans="2:23" ht="20.100000000000001" customHeight="1">
+      <c r="B22" s="37"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="8"/>
+    </row>
+    <row r="23" spans="2:23" ht="20.100000000000001" customHeight="1">
+      <c r="B23" s="35"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="36"/>
+      <c r="Q23" s="8"/>
+    </row>
+    <row r="24" spans="2:23">
+      <c r="B24" s="35"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="36"/>
+      <c r="Q24" s="8"/>
+    </row>
+    <row r="25" spans="2:23">
+      <c r="B25" s="35"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="36"/>
+      <c r="Q25" s="8"/>
+    </row>
+    <row r="26" spans="2:23">
+      <c r="B26" s="39"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="41"/>
+      <c r="L26" s="41"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="41"/>
+      <c r="P26" s="42"/>
+      <c r="Q26" s="8"/>
+    </row>
+    <row r="27" spans="2:23">
+      <c r="B27" s="8"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="8"/>
+      <c r="Q27" s="8"/>
+    </row>
+    <row r="28" spans="2:23">
+      <c r="B28" s="8"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="8"/>
+      <c r="Q28" s="8"/>
+    </row>
+    <row r="29" spans="2:23">
+      <c r="B29" s="8"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
+      <c r="P29" s="8"/>
+      <c r="Q29" s="8"/>
+    </row>
+    <row r="30" spans="2:23">
+      <c r="B30" s="8"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
+      <c r="P30" s="8"/>
+      <c r="Q30" s="8"/>
+    </row>
+    <row r="31" spans="2:23">
+      <c r="B31" s="8"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
+      <c r="P31" s="8"/>
+      <c r="Q31" s="8"/>
+    </row>
+    <row r="32" spans="2:23">
+      <c r="B32" s="8"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
+      <c r="P32" s="8"/>
+      <c r="Q32" s="8"/>
+    </row>
+    <row r="33" spans="2:17">
+      <c r="B33" s="8"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
+      <c r="P33" s="8"/>
+      <c r="Q33" s="8"/>
+    </row>
+    <row r="34" spans="2:17">
+      <c r="B34" s="8"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
+      <c r="P34" s="8"/>
+      <c r="Q34" s="8"/>
+    </row>
+    <row r="35" spans="2:17">
+      <c r="B35" s="8"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
+      <c r="P35" s="8"/>
+      <c r="Q35" s="8"/>
+    </row>
+    <row r="36" spans="2:17">
+      <c r="B36" s="8"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="8"/>
+      <c r="P36" s="8"/>
+      <c r="Q36" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:P1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>